--- a/artfynd/A 37593-2021 artfynd.xlsx
+++ b/artfynd/A 37593-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 37593-2021 artfynd.xlsx
+++ b/artfynd/A 37593-2021 artfynd.xlsx
@@ -3348,10 +3348,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119537241</v>
+        <v>119536059</v>
       </c>
       <c r="B26" t="n">
-        <v>91834</v>
+        <v>57310</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3364,34 +3364,39 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4362</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Dövelmyran, Ly lm</t>
+          <t>Hållängestjärnen, Ly lm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>640636</v>
+        <v>640691</v>
       </c>
       <c r="R26" t="n">
-        <v>7174580</v>
+        <v>7174613</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3423,7 +3428,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3433,7 +3438,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3460,7 +3465,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119536059</v>
+        <v>119536080</v>
       </c>
       <c r="B27" t="n">
         <v>57310</v>
@@ -3505,10 +3510,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>640691</v>
+        <v>640858</v>
       </c>
       <c r="R27" t="n">
-        <v>7174613</v>
+        <v>7174997</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3540,7 +3545,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3550,7 +3555,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3577,10 +3582,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119536080</v>
+        <v>119536254</v>
       </c>
       <c r="B28" t="n">
-        <v>57310</v>
+        <v>91883</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3593,39 +3598,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>5448</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Hållängestjärnen, Ly lm</t>
+          <t>Dövelmyran, Ly lm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>640858</v>
+        <v>640551</v>
       </c>
       <c r="R28" t="n">
-        <v>7174997</v>
+        <v>7174574</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3657,7 +3657,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>16:43</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3667,7 +3667,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>16:43</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3694,10 +3694,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119536254</v>
+        <v>119537241</v>
       </c>
       <c r="B29" t="n">
-        <v>91883</v>
+        <v>91834</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3710,21 +3710,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5448</v>
+        <v>4362</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3734,10 +3734,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>640551</v>
+        <v>640636</v>
       </c>
       <c r="R29" t="n">
-        <v>7174574</v>
+        <v>7174580</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3769,7 +3769,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3779,7 +3779,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3806,10 +3806,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119536610</v>
+        <v>119536615</v>
       </c>
       <c r="B30" t="n">
-        <v>91832</v>
+        <v>92030</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3822,21 +3822,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4361</v>
+        <v>2079</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3846,10 +3846,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>640672</v>
+        <v>640645</v>
       </c>
       <c r="R30" t="n">
-        <v>7174604</v>
+        <v>7174582</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3881,7 +3881,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3918,10 +3918,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119536615</v>
+        <v>119536610</v>
       </c>
       <c r="B31" t="n">
-        <v>92030</v>
+        <v>91832</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3934,21 +3934,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2079</v>
+        <v>4361</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3958,10 +3958,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>640645</v>
+        <v>640672</v>
       </c>
       <c r="R31" t="n">
-        <v>7174582</v>
+        <v>7174604</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -3993,7 +3993,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4003,7 +4003,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4264,10 +4264,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119536263</v>
+        <v>119536319</v>
       </c>
       <c r="B34" t="n">
-        <v>91884</v>
+        <v>91856</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4280,34 +4280,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5449</v>
+        <v>2059</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Dövelmyran, Ly lm</t>
+          <t>Hållängestjärnen, Ly lm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>640635</v>
+        <v>640654</v>
       </c>
       <c r="R34" t="n">
-        <v>7174577</v>
+        <v>7174598</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4339,7 +4339,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4349,7 +4349,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4376,10 +4376,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119536608</v>
+        <v>119536263</v>
       </c>
       <c r="B35" t="n">
-        <v>91832</v>
+        <v>91884</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4392,21 +4392,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4361</v>
+        <v>5449</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4416,10 +4416,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>640549</v>
+        <v>640635</v>
       </c>
       <c r="R35" t="n">
-        <v>7174575</v>
+        <v>7174577</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4451,7 +4451,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4461,7 +4461,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4488,10 +4488,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119536319</v>
+        <v>119536608</v>
       </c>
       <c r="B36" t="n">
-        <v>91856</v>
+        <v>91832</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4504,34 +4504,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2059</v>
+        <v>4361</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Hållängestjärnen, Ly lm</t>
+          <t>Dövelmyran, Ly lm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>640654</v>
+        <v>640549</v>
       </c>
       <c r="R36" t="n">
-        <v>7174598</v>
+        <v>7174575</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4563,7 +4563,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4573,7 +4573,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4941,10 +4941,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119536111</v>
+        <v>119537095</v>
       </c>
       <c r="B40" t="n">
-        <v>57463</v>
+        <v>91840</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4953,47 +4953,38 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Dövelmyran, Ly lm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>640579</v>
+        <v>640519</v>
       </c>
       <c r="R40" t="n">
-        <v>7174575</v>
+        <v>7174657</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -5025,7 +5016,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5035,7 +5026,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5062,10 +5053,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119537095</v>
+        <v>119536056</v>
       </c>
       <c r="B41" t="n">
-        <v>91840</v>
+        <v>57310</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5074,38 +5065,43 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Dövelmyran, Ly lm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>640519</v>
+        <v>640563</v>
       </c>
       <c r="R41" t="n">
-        <v>7174657</v>
+        <v>7174601</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -5137,7 +5133,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5147,7 +5143,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5174,10 +5170,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119536056</v>
+        <v>119536111</v>
       </c>
       <c r="B42" t="n">
-        <v>57310</v>
+        <v>57463</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5190,27 +5186,31 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -5219,10 +5219,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>640563</v>
+        <v>640579</v>
       </c>
       <c r="R42" t="n">
-        <v>7174601</v>
+        <v>7174575</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5254,7 +5254,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD42" t="b">

--- a/artfynd/A 37593-2021 artfynd.xlsx
+++ b/artfynd/A 37593-2021 artfynd.xlsx
@@ -3806,10 +3806,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119536615</v>
+        <v>119536610</v>
       </c>
       <c r="B30" t="n">
-        <v>92030</v>
+        <v>91832</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3822,21 +3822,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2079</v>
+        <v>4361</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3846,10 +3846,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>640645</v>
+        <v>640672</v>
       </c>
       <c r="R30" t="n">
-        <v>7174582</v>
+        <v>7174604</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3881,7 +3881,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3918,10 +3918,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119536610</v>
+        <v>119536615</v>
       </c>
       <c r="B31" t="n">
-        <v>91832</v>
+        <v>92030</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3934,21 +3934,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4361</v>
+        <v>2079</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3958,10 +3958,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>640672</v>
+        <v>640645</v>
       </c>
       <c r="R31" t="n">
-        <v>7174604</v>
+        <v>7174582</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -3993,7 +3993,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4003,7 +4003,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4264,10 +4264,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119536319</v>
+        <v>119536263</v>
       </c>
       <c r="B34" t="n">
-        <v>91856</v>
+        <v>91884</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4280,34 +4280,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>2059</v>
+        <v>5449</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Hållängestjärnen, Ly lm</t>
+          <t>Dövelmyran, Ly lm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>640654</v>
+        <v>640635</v>
       </c>
       <c r="R34" t="n">
-        <v>7174598</v>
+        <v>7174577</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4339,7 +4339,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4349,7 +4349,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4376,10 +4376,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119536263</v>
+        <v>119536608</v>
       </c>
       <c r="B35" t="n">
-        <v>91884</v>
+        <v>91832</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4392,21 +4392,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5449</v>
+        <v>4361</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4416,10 +4416,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>640635</v>
+        <v>640549</v>
       </c>
       <c r="R35" t="n">
-        <v>7174577</v>
+        <v>7174575</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4451,7 +4451,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4461,7 +4461,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4488,10 +4488,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119536608</v>
+        <v>119536319</v>
       </c>
       <c r="B36" t="n">
-        <v>91832</v>
+        <v>91856</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4504,34 +4504,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4361</v>
+        <v>2059</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Dövelmyran, Ly lm</t>
+          <t>Hållängestjärnen, Ly lm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>640549</v>
+        <v>640654</v>
       </c>
       <c r="R36" t="n">
-        <v>7174575</v>
+        <v>7174598</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4563,7 +4563,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4573,7 +4573,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4941,10 +4941,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119537095</v>
+        <v>119536111</v>
       </c>
       <c r="B40" t="n">
-        <v>91840</v>
+        <v>57463</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4953,38 +4953,47 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Dövelmyran, Ly lm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>640519</v>
+        <v>640579</v>
       </c>
       <c r="R40" t="n">
-        <v>7174657</v>
+        <v>7174575</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -5016,7 +5025,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5026,7 +5035,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5053,10 +5062,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119536056</v>
+        <v>119537095</v>
       </c>
       <c r="B41" t="n">
-        <v>57310</v>
+        <v>91840</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5065,43 +5074,38 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Dövelmyran, Ly lm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>640563</v>
+        <v>640519</v>
       </c>
       <c r="R41" t="n">
-        <v>7174601</v>
+        <v>7174657</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -5133,7 +5137,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5143,7 +5147,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5170,10 +5174,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119536111</v>
+        <v>119536056</v>
       </c>
       <c r="B42" t="n">
-        <v>57463</v>
+        <v>57310</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5186,31 +5190,27 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="M42" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -5219,10 +5219,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>640579</v>
+        <v>640563</v>
       </c>
       <c r="R42" t="n">
-        <v>7174575</v>
+        <v>7174601</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5254,7 +5254,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD42" t="b">

--- a/artfynd/A 37593-2021 artfynd.xlsx
+++ b/artfynd/A 37593-2021 artfynd.xlsx
@@ -1994,10 +1994,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119536822</v>
+        <v>119537102</v>
       </c>
       <c r="B14" t="n">
-        <v>91825</v>
+        <v>91840</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2006,38 +2006,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1968</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Bankera violascens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein. : Fr.) Pouzar</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Dövelmyran, Ly lm</t>
+          <t>Hållängestjärnen, Ly lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>640481</v>
+        <v>640739</v>
       </c>
       <c r="R14" t="n">
-        <v>7174700</v>
+        <v>7174587</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2069,7 +2069,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2079,12 +2079,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:54</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Torr tallskog på myrholme</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2111,7 +2106,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119537101</v>
+        <v>119537094</v>
       </c>
       <c r="B15" t="n">
         <v>91840</v>
@@ -2147,14 +2142,14 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Hållängestjärnen, Ly lm</t>
+          <t>Dövelmyran, Ly lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>640678</v>
+        <v>640482</v>
       </c>
       <c r="R15" t="n">
-        <v>7174605</v>
+        <v>7174696</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2186,7 +2181,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2196,7 +2191,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2223,7 +2218,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119537094</v>
+        <v>119537095</v>
       </c>
       <c r="B16" t="n">
         <v>91840</v>
@@ -2263,10 +2258,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>640482</v>
+        <v>640519</v>
       </c>
       <c r="R16" t="n">
-        <v>7174696</v>
+        <v>7174657</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2298,7 +2293,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2308,7 +2303,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2335,10 +2330,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119535999</v>
+        <v>119537150</v>
       </c>
       <c r="B17" t="n">
-        <v>89633</v>
+        <v>77458</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2351,21 +2346,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1962</v>
+        <v>6487</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2375,10 +2370,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>640558</v>
+        <v>640426</v>
       </c>
       <c r="R17" t="n">
-        <v>7174598</v>
+        <v>7174750</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2410,7 +2405,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2420,7 +2415,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2447,10 +2442,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119536609</v>
+        <v>119536058</v>
       </c>
       <c r="B18" t="n">
-        <v>91832</v>
+        <v>57310</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2463,34 +2458,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4361</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Hållängestjärnen, Ly lm</t>
+          <t>Dövelmyran, Ly lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>640652</v>
+        <v>640580</v>
       </c>
       <c r="R18" t="n">
-        <v>7174606</v>
+        <v>7174577</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2522,7 +2522,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2532,7 +2532,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2559,10 +2559,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119536230</v>
+        <v>119535994</v>
       </c>
       <c r="B19" t="n">
-        <v>91463</v>
+        <v>79115</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2575,21 +2575,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4745</v>
+        <v>229821</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2599,10 +2599,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>640561</v>
+        <v>640427</v>
       </c>
       <c r="R19" t="n">
-        <v>7174575</v>
+        <v>7174744</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2634,7 +2634,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2644,7 +2644,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2671,10 +2671,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119536317</v>
+        <v>119537241</v>
       </c>
       <c r="B20" t="n">
-        <v>91856</v>
+        <v>91834</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2687,21 +2687,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2059</v>
+        <v>4362</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2711,10 +2711,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>640556</v>
+        <v>640636</v>
       </c>
       <c r="R20" t="n">
-        <v>7174570</v>
+        <v>7174580</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2746,7 +2746,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2756,7 +2756,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2783,10 +2783,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119535991</v>
+        <v>119536317</v>
       </c>
       <c r="B21" t="n">
-        <v>79144</v>
+        <v>91856</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2799,21 +2799,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6453</v>
+        <v>2059</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2823,10 +2823,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>640638</v>
+        <v>640556</v>
       </c>
       <c r="R21" t="n">
-        <v>7174577</v>
+        <v>7174570</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2868,7 +2868,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2895,10 +2895,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119536057</v>
+        <v>119535999</v>
       </c>
       <c r="B22" t="n">
-        <v>57310</v>
+        <v>89633</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2911,39 +2911,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>1962</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Dövelmyran, Ly lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>640569</v>
+        <v>640558</v>
       </c>
       <c r="R22" t="n">
-        <v>7174576</v>
+        <v>7174598</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2975,7 +2970,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2985,7 +2980,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3012,10 +3007,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119537100</v>
+        <v>119535991</v>
       </c>
       <c r="B23" t="n">
-        <v>91840</v>
+        <v>79144</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3024,25 +3019,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3052,10 +3047,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>640630</v>
+        <v>640638</v>
       </c>
       <c r="R23" t="n">
-        <v>7174575</v>
+        <v>7174577</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3087,7 +3082,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3097,7 +3092,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3124,10 +3119,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119535987</v>
+        <v>119536111</v>
       </c>
       <c r="B24" t="n">
-        <v>90527</v>
+        <v>57463</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3136,38 +3131,47 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5447</v>
+        <v>103021</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Dövelmyran, Ly lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>640555</v>
+        <v>640579</v>
       </c>
       <c r="R24" t="n">
-        <v>7174569</v>
+        <v>7174575</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3199,7 +3203,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3209,7 +3213,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3236,10 +3240,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119535994</v>
+        <v>119536822</v>
       </c>
       <c r="B25" t="n">
-        <v>79115</v>
+        <v>91825</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3252,21 +3256,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>229821</v>
+        <v>1968</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Bankera violascens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Alb. &amp; Schwein. : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3276,10 +3280,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>640427</v>
+        <v>640481</v>
       </c>
       <c r="R25" t="n">
-        <v>7174744</v>
+        <v>7174700</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3311,7 +3315,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3321,7 +3325,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:54</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Torr tallskog på myrholme</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3348,10 +3357,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119536059</v>
+        <v>119536230</v>
       </c>
       <c r="B26" t="n">
-        <v>57310</v>
+        <v>91463</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3364,39 +3373,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>4745</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Hållängestjärnen, Ly lm</t>
+          <t>Dövelmyran, Ly lm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>640691</v>
+        <v>640561</v>
       </c>
       <c r="R26" t="n">
-        <v>7174613</v>
+        <v>7174575</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3428,7 +3432,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3438,7 +3442,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3465,10 +3469,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119536080</v>
+        <v>119537240</v>
       </c>
       <c r="B27" t="n">
-        <v>57310</v>
+        <v>91834</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3481,39 +3485,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>4362</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Hållängestjärnen, Ly lm</t>
+          <t>Dövelmyran, Ly lm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>640858</v>
+        <v>640548</v>
       </c>
       <c r="R27" t="n">
-        <v>7174997</v>
+        <v>7174573</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3545,7 +3544,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>16:43</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3555,7 +3554,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>16:43</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3582,10 +3581,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119536254</v>
+        <v>119536609</v>
       </c>
       <c r="B28" t="n">
-        <v>91883</v>
+        <v>91832</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3598,34 +3597,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5448</v>
+        <v>4361</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Dövelmyran, Ly lm</t>
+          <t>Hållängestjärnen, Ly lm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>640551</v>
+        <v>640652</v>
       </c>
       <c r="R28" t="n">
-        <v>7174574</v>
+        <v>7174606</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3657,7 +3656,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3667,7 +3666,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3694,10 +3693,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119537241</v>
+        <v>119536080</v>
       </c>
       <c r="B29" t="n">
-        <v>91834</v>
+        <v>57310</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3710,34 +3709,39 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4362</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Dövelmyran, Ly lm</t>
+          <t>Hållängestjärnen, Ly lm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>640636</v>
+        <v>640858</v>
       </c>
       <c r="R29" t="n">
-        <v>7174580</v>
+        <v>7174997</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3769,7 +3773,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3779,7 +3783,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3806,7 +3810,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119536610</v>
+        <v>119536607</v>
       </c>
       <c r="B30" t="n">
         <v>91832</v>
@@ -3842,14 +3846,14 @@
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Hållängestjärnen, Ly lm</t>
+          <t>Dövelmyran, Ly lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>640672</v>
+        <v>640508</v>
       </c>
       <c r="R30" t="n">
-        <v>7174604</v>
+        <v>7174659</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3881,7 +3885,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3891,7 +3895,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3918,10 +3922,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119536615</v>
+        <v>119536056</v>
       </c>
       <c r="B31" t="n">
-        <v>92030</v>
+        <v>57310</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3934,34 +3938,39 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2079</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Hållängestjärnen, Ly lm</t>
+          <t>Dövelmyran, Ly lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>640645</v>
+        <v>640563</v>
       </c>
       <c r="R31" t="n">
-        <v>7174582</v>
+        <v>7174601</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -3993,7 +4002,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4003,7 +4012,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4030,10 +4039,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119536060</v>
+        <v>119536254</v>
       </c>
       <c r="B32" t="n">
-        <v>57310</v>
+        <v>91883</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4046,39 +4055,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>5448</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Hållängestjärnen, Ly lm</t>
+          <t>Dövelmyran, Ly lm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>640678</v>
+        <v>640551</v>
       </c>
       <c r="R32" t="n">
-        <v>7174604</v>
+        <v>7174574</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4110,7 +4114,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4120,7 +4124,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4147,10 +4151,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119536079</v>
+        <v>119537100</v>
       </c>
       <c r="B33" t="n">
-        <v>57310</v>
+        <v>91840</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4159,43 +4163,38 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Hållängestjärnen, Ly lm</t>
+          <t>Dövelmyran, Ly lm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>640904</v>
+        <v>640630</v>
       </c>
       <c r="R33" t="n">
-        <v>7174982</v>
+        <v>7174575</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4227,7 +4226,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4237,7 +4236,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4264,10 +4263,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119536263</v>
+        <v>119537242</v>
       </c>
       <c r="B34" t="n">
-        <v>91884</v>
+        <v>91834</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4280,34 +4279,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5449</v>
+        <v>4362</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Dövelmyran, Ly lm</t>
+          <t>Hållängestjärnen, Ly lm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>640635</v>
+        <v>640739</v>
       </c>
       <c r="R34" t="n">
-        <v>7174577</v>
+        <v>7174586</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4339,7 +4338,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4349,7 +4348,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4376,10 +4375,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119536608</v>
+        <v>119536057</v>
       </c>
       <c r="B35" t="n">
-        <v>91832</v>
+        <v>57310</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4392,34 +4391,39 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4361</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Dövelmyran, Ly lm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>640549</v>
+        <v>640569</v>
       </c>
       <c r="R35" t="n">
-        <v>7174575</v>
+        <v>7174576</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4451,7 +4455,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4461,7 +4465,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4488,10 +4492,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119536319</v>
+        <v>119536608</v>
       </c>
       <c r="B36" t="n">
-        <v>91856</v>
+        <v>91832</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4504,34 +4508,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2059</v>
+        <v>4361</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Hållängestjärnen, Ly lm</t>
+          <t>Dövelmyran, Ly lm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>640654</v>
+        <v>640549</v>
       </c>
       <c r="R36" t="n">
-        <v>7174598</v>
+        <v>7174575</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4563,7 +4567,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4573,7 +4577,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4600,10 +4604,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119537240</v>
+        <v>119537054</v>
       </c>
       <c r="B37" t="n">
-        <v>91834</v>
+        <v>78171</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4616,21 +4620,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4362</v>
+        <v>353</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4640,7 +4644,7 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>640548</v>
+        <v>640551</v>
       </c>
       <c r="R37" t="n">
         <v>7174573</v>
@@ -4675,7 +4679,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4685,7 +4689,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4712,10 +4716,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119536055</v>
+        <v>119535987</v>
       </c>
       <c r="B38" t="n">
-        <v>57310</v>
+        <v>90527</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4724,43 +4728,38 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Dövelmyran, Ly lm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>640521</v>
+        <v>640555</v>
       </c>
       <c r="R38" t="n">
-        <v>7174659</v>
+        <v>7174569</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4792,7 +4791,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4802,7 +4801,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4829,10 +4828,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119537150</v>
+        <v>119537097</v>
       </c>
       <c r="B39" t="n">
-        <v>77458</v>
+        <v>91840</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4841,25 +4840,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6487</v>
+        <v>4364</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4869,10 +4868,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>640426</v>
+        <v>640566</v>
       </c>
       <c r="R39" t="n">
-        <v>7174750</v>
+        <v>7174602</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4904,7 +4903,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4914,7 +4913,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4941,10 +4940,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119536111</v>
+        <v>119537101</v>
       </c>
       <c r="B40" t="n">
-        <v>57463</v>
+        <v>91840</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4953,47 +4952,38 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Dövelmyran, Ly lm</t>
+          <t>Hållängestjärnen, Ly lm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>640579</v>
+        <v>640678</v>
       </c>
       <c r="R40" t="n">
-        <v>7174575</v>
+        <v>7174605</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -5025,7 +5015,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5035,7 +5025,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5062,10 +5052,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119537095</v>
+        <v>119536079</v>
       </c>
       <c r="B41" t="n">
-        <v>91840</v>
+        <v>57310</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5074,38 +5064,43 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Dövelmyran, Ly lm</t>
+          <t>Hållängestjärnen, Ly lm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>640519</v>
+        <v>640904</v>
       </c>
       <c r="R41" t="n">
-        <v>7174657</v>
+        <v>7174982</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -5137,7 +5132,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5147,7 +5142,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5174,7 +5169,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119536056</v>
+        <v>119536059</v>
       </c>
       <c r="B42" t="n">
         <v>57310</v>
@@ -5210,19 +5205,19 @@
       <c r="I42" t="inlineStr"/>
       <c r="M42" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Dövelmyran, Ly lm</t>
+          <t>Hållängestjärnen, Ly lm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>640563</v>
+        <v>640691</v>
       </c>
       <c r="R42" t="n">
-        <v>7174601</v>
+        <v>7174613</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5254,7 +5249,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5264,7 +5259,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5291,10 +5286,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119537054</v>
+        <v>119536319</v>
       </c>
       <c r="B43" t="n">
-        <v>78171</v>
+        <v>91856</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5307,34 +5302,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>353</v>
+        <v>2059</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Dövelmyran, Ly lm</t>
+          <t>Hållängestjärnen, Ly lm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>640551</v>
+        <v>640654</v>
       </c>
       <c r="R43" t="n">
-        <v>7174573</v>
+        <v>7174598</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5366,7 +5361,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5376,7 +5371,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5403,10 +5398,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119537242</v>
+        <v>119536263</v>
       </c>
       <c r="B44" t="n">
-        <v>91834</v>
+        <v>91884</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5419,34 +5414,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4362</v>
+        <v>5449</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Hållängestjärnen, Ly lm</t>
+          <t>Dövelmyran, Ly lm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>640739</v>
+        <v>640635</v>
       </c>
       <c r="R44" t="n">
-        <v>7174586</v>
+        <v>7174577</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5478,7 +5473,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5488,7 +5483,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5515,10 +5510,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119537102</v>
+        <v>119536610</v>
       </c>
       <c r="B45" t="n">
-        <v>91840</v>
+        <v>91832</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5527,25 +5522,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5555,10 +5550,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>640739</v>
+        <v>640672</v>
       </c>
       <c r="R45" t="n">
-        <v>7174587</v>
+        <v>7174604</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5590,7 +5585,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5600,7 +5595,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5627,10 +5622,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119537097</v>
+        <v>119536060</v>
       </c>
       <c r="B46" t="n">
-        <v>91840</v>
+        <v>57310</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5639,38 +5634,43 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Dövelmyran, Ly lm</t>
+          <t>Hållängestjärnen, Ly lm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>640566</v>
+        <v>640678</v>
       </c>
       <c r="R46" t="n">
-        <v>7174602</v>
+        <v>7174604</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5702,7 +5702,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5712,7 +5712,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5739,10 +5739,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119536607</v>
+        <v>119537093</v>
       </c>
       <c r="B47" t="n">
-        <v>91832</v>
+        <v>91840</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5751,25 +5751,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5779,10 +5779,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>640508</v>
+        <v>640429</v>
       </c>
       <c r="R47" t="n">
-        <v>7174659</v>
+        <v>7174746</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5814,7 +5814,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5824,7 +5824,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5851,10 +5851,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119537093</v>
+        <v>119536055</v>
       </c>
       <c r="B48" t="n">
-        <v>91840</v>
+        <v>57310</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5863,38 +5863,43 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Dövelmyran, Ly lm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>640429</v>
+        <v>640521</v>
       </c>
       <c r="R48" t="n">
-        <v>7174746</v>
+        <v>7174659</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -5926,7 +5931,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5936,7 +5941,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5963,10 +5968,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119536058</v>
+        <v>119536615</v>
       </c>
       <c r="B49" t="n">
-        <v>57310</v>
+        <v>92030</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5979,39 +5984,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>2079</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Dövelmyran, Ly lm</t>
+          <t>Hållängestjärnen, Ly lm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>640580</v>
+        <v>640645</v>
       </c>
       <c r="R49" t="n">
-        <v>7174577</v>
+        <v>7174582</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -6043,7 +6043,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6053,7 +6053,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD49" t="b">

--- a/artfynd/A 37593-2021 artfynd.xlsx
+++ b/artfynd/A 37593-2021 artfynd.xlsx
@@ -2895,10 +2895,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119535999</v>
+        <v>119536111</v>
       </c>
       <c r="B22" t="n">
-        <v>89633</v>
+        <v>57463</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2911,34 +2911,43 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1962</v>
+        <v>103021</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Dövelmyran, Ly lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>640558</v>
+        <v>640579</v>
       </c>
       <c r="R22" t="n">
-        <v>7174598</v>
+        <v>7174575</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2970,7 +2979,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2980,7 +2989,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3119,10 +3128,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119536111</v>
+        <v>119535999</v>
       </c>
       <c r="B24" t="n">
-        <v>57463</v>
+        <v>89633</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3135,43 +3144,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103021</v>
+        <v>1962</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Parmasto) Bondartseva</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Dövelmyran, Ly lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>640579</v>
+        <v>640558</v>
       </c>
       <c r="R24" t="n">
-        <v>7174575</v>
+        <v>7174598</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3203,7 +3203,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3213,7 +3213,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3810,10 +3810,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119536607</v>
+        <v>119536056</v>
       </c>
       <c r="B30" t="n">
-        <v>91832</v>
+        <v>57310</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3826,34 +3826,39 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4361</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Dövelmyran, Ly lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>640508</v>
+        <v>640563</v>
       </c>
       <c r="R30" t="n">
-        <v>7174659</v>
+        <v>7174601</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3885,7 +3890,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3895,7 +3900,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3922,10 +3927,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119536056</v>
+        <v>119536607</v>
       </c>
       <c r="B31" t="n">
-        <v>57310</v>
+        <v>91832</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3938,39 +3943,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>4361</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Dövelmyran, Ly lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>640563</v>
+        <v>640508</v>
       </c>
       <c r="R31" t="n">
-        <v>7174601</v>
+        <v>7174659</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4002,7 +4002,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4012,7 +4012,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4039,10 +4039,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119536254</v>
+        <v>119537100</v>
       </c>
       <c r="B32" t="n">
-        <v>91883</v>
+        <v>91840</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4051,25 +4051,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5448</v>
+        <v>4364</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4079,10 +4079,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>640551</v>
+        <v>640630</v>
       </c>
       <c r="R32" t="n">
-        <v>7174574</v>
+        <v>7174575</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4114,7 +4114,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4124,7 +4124,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4151,10 +4151,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119537100</v>
+        <v>119536254</v>
       </c>
       <c r="B33" t="n">
-        <v>91840</v>
+        <v>91883</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4163,25 +4163,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4364</v>
+        <v>5448</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4191,10 +4191,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>640630</v>
+        <v>640551</v>
       </c>
       <c r="R33" t="n">
-        <v>7174575</v>
+        <v>7174574</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4226,7 +4226,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD33" t="b">

--- a/artfynd/A 37593-2021 artfynd.xlsx
+++ b/artfynd/A 37593-2021 artfynd.xlsx
@@ -1994,10 +1994,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119537102</v>
+        <v>119536263</v>
       </c>
       <c r="B14" t="n">
-        <v>91840</v>
+        <v>91884</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2006,38 +2006,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Hållängestjärnen, Ly lm</t>
+          <t>Dövelmyran, Ly lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>640739</v>
+        <v>640635</v>
       </c>
       <c r="R14" t="n">
-        <v>7174587</v>
+        <v>7174577</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2069,7 +2069,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2079,7 +2079,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2106,10 +2106,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119537094</v>
+        <v>119536822</v>
       </c>
       <c r="B15" t="n">
-        <v>91840</v>
+        <v>91825</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2118,25 +2118,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4364</v>
+        <v>1968</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bankera violascens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Alb. &amp; Schwein. : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2146,10 +2146,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>640482</v>
+        <v>640481</v>
       </c>
       <c r="R15" t="n">
-        <v>7174696</v>
+        <v>7174700</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2191,7 +2191,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>10:54</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Torr tallskog på myrholme</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2218,7 +2223,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119537095</v>
+        <v>119537093</v>
       </c>
       <c r="B16" t="n">
         <v>91840</v>
@@ -2258,10 +2263,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>640519</v>
+        <v>640429</v>
       </c>
       <c r="R16" t="n">
-        <v>7174657</v>
+        <v>7174746</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2293,7 +2298,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2303,7 +2308,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2442,7 +2447,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119536058</v>
+        <v>119536059</v>
       </c>
       <c r="B18" t="n">
         <v>57310</v>
@@ -2478,19 +2483,19 @@
       <c r="I18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Dövelmyran, Ly lm</t>
+          <t>Hållängestjärnen, Ly lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>640580</v>
+        <v>640691</v>
       </c>
       <c r="R18" t="n">
-        <v>7174577</v>
+        <v>7174613</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2522,7 +2527,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2532,7 +2537,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2559,10 +2564,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119535994</v>
+        <v>119536111</v>
       </c>
       <c r="B19" t="n">
-        <v>79115</v>
+        <v>57463</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2575,34 +2580,43 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>229821</v>
+        <v>103021</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Dövelmyran, Ly lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>640427</v>
+        <v>640579</v>
       </c>
       <c r="R19" t="n">
-        <v>7174744</v>
+        <v>7174575</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2634,7 +2648,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2644,7 +2658,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2671,10 +2685,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119537241</v>
+        <v>119536615</v>
       </c>
       <c r="B20" t="n">
-        <v>91834</v>
+        <v>92030</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2687,34 +2701,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4362</v>
+        <v>2079</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Dövelmyran, Ly lm</t>
+          <t>Hållängestjärnen, Ly lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>640636</v>
+        <v>640645</v>
       </c>
       <c r="R20" t="n">
-        <v>7174580</v>
+        <v>7174582</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2746,7 +2760,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2756,7 +2770,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2783,10 +2797,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119536317</v>
+        <v>119537242</v>
       </c>
       <c r="B21" t="n">
-        <v>91856</v>
+        <v>91834</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2799,34 +2813,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2059</v>
+        <v>4362</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Dövelmyran, Ly lm</t>
+          <t>Hållängestjärnen, Ly lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>640556</v>
+        <v>640739</v>
       </c>
       <c r="R21" t="n">
-        <v>7174570</v>
+        <v>7174586</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2858,7 +2872,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2868,7 +2882,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2895,10 +2909,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119536111</v>
+        <v>119536055</v>
       </c>
       <c r="B22" t="n">
-        <v>57463</v>
+        <v>57310</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2911,31 +2925,27 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2944,10 +2954,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>640579</v>
+        <v>640521</v>
       </c>
       <c r="R22" t="n">
-        <v>7174575</v>
+        <v>7174659</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2979,7 +2989,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2989,7 +2999,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3016,10 +3026,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119535991</v>
+        <v>119535987</v>
       </c>
       <c r="B23" t="n">
-        <v>79144</v>
+        <v>90527</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3028,25 +3038,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6453</v>
+        <v>5447</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3056,10 +3066,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>640638</v>
+        <v>640555</v>
       </c>
       <c r="R23" t="n">
-        <v>7174577</v>
+        <v>7174569</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3091,7 +3101,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3101,7 +3111,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3128,10 +3138,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119535999</v>
+        <v>119535994</v>
       </c>
       <c r="B24" t="n">
-        <v>89633</v>
+        <v>79115</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3144,21 +3154,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1962</v>
+        <v>229821</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3168,10 +3178,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>640558</v>
+        <v>640427</v>
       </c>
       <c r="R24" t="n">
-        <v>7174598</v>
+        <v>7174744</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3203,7 +3213,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3213,7 +3223,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3240,10 +3250,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119536822</v>
+        <v>119537097</v>
       </c>
       <c r="B25" t="n">
-        <v>91825</v>
+        <v>91840</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3252,25 +3262,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1968</v>
+        <v>4364</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Bankera violascens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein. : Fr.) Pouzar</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3280,10 +3290,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>640481</v>
+        <v>640566</v>
       </c>
       <c r="R25" t="n">
-        <v>7174700</v>
+        <v>7174602</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3315,7 +3325,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3325,12 +3335,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:54</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Torr tallskog på myrholme</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3357,10 +3362,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119536230</v>
+        <v>119536608</v>
       </c>
       <c r="B26" t="n">
-        <v>91463</v>
+        <v>91832</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3373,21 +3378,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4745</v>
+        <v>4361</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3397,7 +3402,7 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>640561</v>
+        <v>640549</v>
       </c>
       <c r="R26" t="n">
         <v>7174575</v>
@@ -3432,7 +3437,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3442,7 +3447,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3469,10 +3474,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119537240</v>
+        <v>119536058</v>
       </c>
       <c r="B27" t="n">
-        <v>91834</v>
+        <v>57310</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3485,34 +3490,39 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4362</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Dövelmyran, Ly lm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>640548</v>
+        <v>640580</v>
       </c>
       <c r="R27" t="n">
-        <v>7174573</v>
+        <v>7174577</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3544,7 +3554,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3554,7 +3564,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3581,10 +3591,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119536609</v>
+        <v>119536317</v>
       </c>
       <c r="B28" t="n">
-        <v>91832</v>
+        <v>91856</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3597,34 +3607,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4361</v>
+        <v>2059</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Hållängestjärnen, Ly lm</t>
+          <t>Dövelmyran, Ly lm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>640652</v>
+        <v>640556</v>
       </c>
       <c r="R28" t="n">
-        <v>7174606</v>
+        <v>7174570</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3656,7 +3666,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3666,7 +3676,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3693,10 +3703,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119536080</v>
+        <v>119536230</v>
       </c>
       <c r="B29" t="n">
-        <v>57310</v>
+        <v>91463</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3709,39 +3719,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>4745</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Hållängestjärnen, Ly lm</t>
+          <t>Dövelmyran, Ly lm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>640858</v>
+        <v>640561</v>
       </c>
       <c r="R29" t="n">
-        <v>7174997</v>
+        <v>7174575</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3773,7 +3778,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>16:43</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3783,7 +3788,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>16:43</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3810,10 +3815,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119536056</v>
+        <v>119537054</v>
       </c>
       <c r="B30" t="n">
-        <v>57310</v>
+        <v>78171</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3826,39 +3831,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>353</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Dövelmyran, Ly lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>640563</v>
+        <v>640551</v>
       </c>
       <c r="R30" t="n">
-        <v>7174601</v>
+        <v>7174573</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3890,7 +3890,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3900,7 +3900,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3927,10 +3927,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119536607</v>
+        <v>119537101</v>
       </c>
       <c r="B31" t="n">
-        <v>91832</v>
+        <v>91840</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3939,38 +3939,38 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Dövelmyran, Ly lm</t>
+          <t>Hållängestjärnen, Ly lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>640508</v>
+        <v>640678</v>
       </c>
       <c r="R31" t="n">
-        <v>7174659</v>
+        <v>7174605</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4002,7 +4002,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4012,7 +4012,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4039,10 +4039,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119537100</v>
+        <v>119536057</v>
       </c>
       <c r="B32" t="n">
-        <v>91840</v>
+        <v>57310</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4051,38 +4051,43 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Dövelmyran, Ly lm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>640630</v>
+        <v>640569</v>
       </c>
       <c r="R32" t="n">
-        <v>7174575</v>
+        <v>7174576</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4114,7 +4119,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4124,7 +4129,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4151,10 +4156,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119536254</v>
+        <v>119536080</v>
       </c>
       <c r="B33" t="n">
-        <v>91883</v>
+        <v>57310</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4167,34 +4172,39 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5448</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Dövelmyran, Ly lm</t>
+          <t>Hållängestjärnen, Ly lm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>640551</v>
+        <v>640858</v>
       </c>
       <c r="R33" t="n">
-        <v>7174574</v>
+        <v>7174997</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4226,7 +4236,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4236,7 +4246,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4263,10 +4273,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119537242</v>
+        <v>119536060</v>
       </c>
       <c r="B34" t="n">
-        <v>91834</v>
+        <v>57310</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4279,34 +4289,39 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4362</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Hållängestjärnen, Ly lm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>640739</v>
+        <v>640678</v>
       </c>
       <c r="R34" t="n">
-        <v>7174586</v>
+        <v>7174604</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4338,7 +4353,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4348,7 +4363,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4375,10 +4390,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119536057</v>
+        <v>119535999</v>
       </c>
       <c r="B35" t="n">
-        <v>57310</v>
+        <v>89633</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4391,39 +4406,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>1962</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Dövelmyran, Ly lm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>640569</v>
+        <v>640558</v>
       </c>
       <c r="R35" t="n">
-        <v>7174576</v>
+        <v>7174598</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4455,7 +4465,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4465,7 +4475,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4492,7 +4502,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119536608</v>
+        <v>119536609</v>
       </c>
       <c r="B36" t="n">
         <v>91832</v>
@@ -4528,14 +4538,14 @@
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Dövelmyran, Ly lm</t>
+          <t>Hållängestjärnen, Ly lm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>640549</v>
+        <v>640652</v>
       </c>
       <c r="R36" t="n">
-        <v>7174575</v>
+        <v>7174606</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4567,7 +4577,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4577,7 +4587,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4604,10 +4614,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119537054</v>
+        <v>119537102</v>
       </c>
       <c r="B37" t="n">
-        <v>78171</v>
+        <v>91840</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4616,38 +4626,38 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Dövelmyran, Ly lm</t>
+          <t>Hållängestjärnen, Ly lm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>640551</v>
+        <v>640739</v>
       </c>
       <c r="R37" t="n">
-        <v>7174573</v>
+        <v>7174587</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4679,7 +4689,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4689,7 +4699,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4716,10 +4726,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119535987</v>
+        <v>119537094</v>
       </c>
       <c r="B38" t="n">
-        <v>90527</v>
+        <v>91840</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4732,21 +4742,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5447</v>
+        <v>4364</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4756,10 +4766,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>640555</v>
+        <v>640482</v>
       </c>
       <c r="R38" t="n">
-        <v>7174569</v>
+        <v>7174696</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4791,7 +4801,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4801,7 +4811,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4828,10 +4838,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119537097</v>
+        <v>119536607</v>
       </c>
       <c r="B39" t="n">
-        <v>91840</v>
+        <v>91832</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4840,25 +4850,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4868,10 +4878,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>640566</v>
+        <v>640508</v>
       </c>
       <c r="R39" t="n">
-        <v>7174602</v>
+        <v>7174659</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4903,7 +4913,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4913,7 +4923,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4940,10 +4950,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119537101</v>
+        <v>119537241</v>
       </c>
       <c r="B40" t="n">
-        <v>91840</v>
+        <v>91834</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4952,38 +4962,38 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Hållängestjärnen, Ly lm</t>
+          <t>Dövelmyran, Ly lm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>640678</v>
+        <v>640636</v>
       </c>
       <c r="R40" t="n">
-        <v>7174605</v>
+        <v>7174580</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -5015,7 +5025,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5025,7 +5035,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5052,10 +5062,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119536079</v>
+        <v>119536319</v>
       </c>
       <c r="B41" t="n">
-        <v>57310</v>
+        <v>91856</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5068,39 +5078,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>2059</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Hållängestjärnen, Ly lm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>640904</v>
+        <v>640654</v>
       </c>
       <c r="R41" t="n">
-        <v>7174982</v>
+        <v>7174598</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -5132,7 +5137,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5142,7 +5147,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5169,10 +5174,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119536059</v>
+        <v>119536610</v>
       </c>
       <c r="B42" t="n">
-        <v>57310</v>
+        <v>91832</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5185,39 +5190,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>4361</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Hållängestjärnen, Ly lm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>640691</v>
+        <v>640672</v>
       </c>
       <c r="R42" t="n">
-        <v>7174613</v>
+        <v>7174604</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5249,7 +5249,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5259,7 +5259,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5286,10 +5286,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119536319</v>
+        <v>119537095</v>
       </c>
       <c r="B43" t="n">
-        <v>91856</v>
+        <v>91840</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5298,38 +5298,38 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Hållängestjärnen, Ly lm</t>
+          <t>Dövelmyran, Ly lm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>640654</v>
+        <v>640519</v>
       </c>
       <c r="R43" t="n">
-        <v>7174598</v>
+        <v>7174657</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5361,7 +5361,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5371,7 +5371,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5398,10 +5398,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119536263</v>
+        <v>119536254</v>
       </c>
       <c r="B44" t="n">
-        <v>91884</v>
+        <v>91883</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5414,21 +5414,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5449</v>
+        <v>5448</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5438,10 +5438,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>640635</v>
+        <v>640551</v>
       </c>
       <c r="R44" t="n">
-        <v>7174577</v>
+        <v>7174574</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5473,7 +5473,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5483,7 +5483,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5510,10 +5510,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119536610</v>
+        <v>119535991</v>
       </c>
       <c r="B45" t="n">
-        <v>91832</v>
+        <v>79144</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5526,34 +5526,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4361</v>
+        <v>6453</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Hållängestjärnen, Ly lm</t>
+          <t>Dövelmyran, Ly lm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>640672</v>
+        <v>640638</v>
       </c>
       <c r="R45" t="n">
-        <v>7174604</v>
+        <v>7174577</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5585,7 +5585,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5595,7 +5595,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5622,10 +5622,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119536060</v>
+        <v>119537240</v>
       </c>
       <c r="B46" t="n">
-        <v>57310</v>
+        <v>91834</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5638,39 +5638,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>4362</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Hållängestjärnen, Ly lm</t>
+          <t>Dövelmyran, Ly lm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>640678</v>
+        <v>640548</v>
       </c>
       <c r="R46" t="n">
-        <v>7174604</v>
+        <v>7174573</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5702,7 +5697,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5712,7 +5707,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5739,10 +5734,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119537093</v>
+        <v>119536056</v>
       </c>
       <c r="B47" t="n">
-        <v>91840</v>
+        <v>57310</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5751,38 +5746,43 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Dövelmyran, Ly lm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>640429</v>
+        <v>640563</v>
       </c>
       <c r="R47" t="n">
-        <v>7174746</v>
+        <v>7174601</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5814,7 +5814,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5824,7 +5824,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5851,10 +5851,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119536055</v>
+        <v>119537100</v>
       </c>
       <c r="B48" t="n">
-        <v>57310</v>
+        <v>91840</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5863,43 +5863,38 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Dövelmyran, Ly lm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>640521</v>
+        <v>640630</v>
       </c>
       <c r="R48" t="n">
-        <v>7174659</v>
+        <v>7174575</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -5931,7 +5926,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5941,7 +5936,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5968,10 +5963,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119536615</v>
+        <v>119536079</v>
       </c>
       <c r="B49" t="n">
-        <v>92030</v>
+        <v>57310</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5984,34 +5979,39 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>2079</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Hållängestjärnen, Ly lm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>640645</v>
+        <v>640904</v>
       </c>
       <c r="R49" t="n">
-        <v>7174582</v>
+        <v>7174982</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -6043,7 +6043,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6053,7 +6053,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AD49" t="b">
